--- a/output/laminas_comunales/comunal_i_ingr_a_2022_antofagasta.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2022_antofagasta.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>1309131.25</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>1280408.38</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>1199445.88</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>1137302.12</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>1131777.25</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>1065980.38</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -474,9 +451,6 @@
       <c r="B8">
         <v>1038321.06</v>
       </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,9 +461,6 @@
       <c r="B9">
         <v>992715.8100000001</v>
       </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -499,9 +470,6 @@
       </c>
       <c r="B10">
         <v>979419.1899999999</v>
-      </c>
-      <c r="F10" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_a_2022_antofagasta.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2022_antofagasta.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -391,6 +391,15 @@
       <c r="B2">
         <v>1309131.25</v>
       </c>
+      <c r="C2">
+        <v>1179795.25</v>
+      </c>
+      <c r="D2">
+        <v>129336</v>
+      </c>
+      <c r="E2">
+        <v>10.96258015956582</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -401,74 +410,147 @@
       <c r="B3">
         <v>1280408.38</v>
       </c>
+      <c r="C3">
+        <v>1160151.5</v>
+      </c>
+      <c r="D3">
+        <v>120256.8799999999</v>
+      </c>
+      <c r="E3">
+        <v>10.36561862825673</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>María Elena</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B4">
-        <v>1199445.88</v>
+        <v>1271792.12</v>
+      </c>
+      <c r="C4">
+        <v>1147628.5</v>
+      </c>
+      <c r="D4">
+        <v>124163.6200000001</v>
+      </c>
+      <c r="E4">
+        <v>10.81914748544499</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mejillones</t>
+          <t>María Elena</t>
         </is>
       </c>
       <c r="B5">
-        <v>1137302.12</v>
+        <v>1199445.88</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tocopilla</t>
+          <t>Mejillones</t>
         </is>
       </c>
       <c r="B6">
-        <v>1131777.25</v>
+        <v>1137302.12</v>
+      </c>
+      <c r="C6">
+        <v>969235.75</v>
+      </c>
+      <c r="D6">
+        <v>168066.3700000001</v>
+      </c>
+      <c r="E6">
+        <v>17.34009192294032</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Taltal</t>
+          <t>Tocopilla</t>
         </is>
       </c>
       <c r="B7">
-        <v>1065980.38</v>
+        <v>1131777.25</v>
+      </c>
+      <c r="C7">
+        <v>993307.5600000001</v>
+      </c>
+      <c r="D7">
+        <v>138469.6899999999</v>
+      </c>
+      <c r="E7">
+        <v>13.9402633762296</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sierra Gorda</t>
+          <t>Taltal</t>
         </is>
       </c>
       <c r="B8">
-        <v>1038321.06</v>
+        <v>1065980.38</v>
+      </c>
+      <c r="C8">
+        <v>949264.5600000001</v>
+      </c>
+      <c r="D8">
+        <v>116715.8199999998</v>
+      </c>
+      <c r="E8">
+        <v>12.2953942365656</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>San Pedro de Atacama</t>
+          <t>Sierra Gorda</t>
         </is>
       </c>
       <c r="B9">
-        <v>992715.8100000001</v>
+        <v>1038321.06</v>
+      </c>
+      <c r="C9">
+        <v>968818.62</v>
+      </c>
+      <c r="D9">
+        <v>69502.44000000006</v>
+      </c>
+      <c r="E9">
+        <v>7.173937263922525</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>San Pedro de Atacama</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>992715.8100000001</v>
+      </c>
+      <c r="C10">
+        <v>841165.9399999999</v>
+      </c>
+      <c r="D10">
+        <v>151549.8700000001</v>
+      </c>
+      <c r="E10">
+        <v>18.01664366010827</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Ollagüe</t>
         </is>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>979419.1899999999</v>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_i_ingr_a_2022_antofagasta.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_a_2022_antofagasta.xlsx
@@ -561,7 +561,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -570,20 +570,12 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>1280408.38</v>
+          <t>María Elena</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -592,48 +584,33 @@
           <t>Calama</t>
         </is>
       </c>
-      <c r="B3">
-        <v>1309131.25</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>María Elena</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>1199445.88</v>
+          <t>Tocopilla</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mejillones</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>1137302.12</v>
+          <t>Antofagasta</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ollagüe</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>979419.1899999999</v>
+          <t>Mejillones</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>San Pedro de Atacama</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>992715.8100000001</v>
+          <t>Taltal</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -642,28 +619,19 @@
           <t>Sierra Gorda</t>
         </is>
       </c>
-      <c r="B8">
-        <v>1038321.06</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Taltal</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>1065980.38</v>
+          <t>San Pedro de Atacama</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tocopilla</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>1131777.25</v>
+          <t>Ollagüe</t>
+        </is>
       </c>
     </row>
   </sheetData>
